--- a/data/trans_dic/IP15-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,9; 20,56</t>
+          <t>9,83; 20,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,56; 31,29</t>
+          <t>17,03; 31,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 27,95</t>
+          <t>12,72; 26,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,8; 30,88</t>
+          <t>17,42; 30,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,23; 29,52</t>
+          <t>14,89; 29,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 32,63</t>
+          <t>17,3; 32,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,85; 24,5</t>
+          <t>12,09; 24,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,57; 30,61</t>
+          <t>16,37; 30,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,13; 22,44</t>
+          <t>14,21; 22,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,36; 30,36</t>
+          <t>18,32; 29,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,92; 23,42</t>
+          <t>13,75; 23,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,85; 29,12</t>
+          <t>18,51; 28,85</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,86; 30,24</t>
+          <t>15,74; 30,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 31,87</t>
+          <t>17,59; 33,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 17,22</t>
+          <t>7,51; 17,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,89; 32,6</t>
+          <t>18,26; 32,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 28,57</t>
+          <t>14,11; 27,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 19,75</t>
+          <t>7,79; 19,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 23,59</t>
+          <t>11,82; 23,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 33,8</t>
+          <t>16,89; 32,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,38; 26,81</t>
+          <t>16,73; 26,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,49; 23,27</t>
+          <t>14,41; 23,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,4; 18,18</t>
+          <t>10,73; 18,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,59; 30,34</t>
+          <t>19,42; 30,28</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 24,69</t>
+          <t>10,41; 24,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 20,15</t>
+          <t>7,96; 20,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 22,28</t>
+          <t>8,73; 22,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,42; 28,89</t>
+          <t>11,33; 29,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,7; 29,15</t>
+          <t>16,03; 29,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 21,66</t>
+          <t>8,56; 21,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 21,53</t>
+          <t>7,74; 20,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,59; 36,89</t>
+          <t>18,59; 37,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,15; 25,8</t>
+          <t>15,21; 25,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 18,48</t>
+          <t>9,85; 18,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 19,35</t>
+          <t>9,8; 19,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,12; 30,6</t>
+          <t>17,16; 31,27</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,25; 23,55</t>
+          <t>14,48; 23,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 28,47</t>
+          <t>18,9; 28,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,78; 25,66</t>
+          <t>16,87; 25,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,2; 59,15</t>
+          <t>23,44; 58,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,71</t>
+          <t>15,08; 24,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,05; 30,77</t>
+          <t>21,11; 31,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,33; 21,16</t>
+          <t>12,66; 21,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,27; 31,83</t>
+          <t>19,97; 31,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,92; 22,3</t>
+          <t>15,73; 22,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,63; 28,23</t>
+          <t>21,56; 28,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 21,68</t>
+          <t>15,93; 21,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 43,59</t>
+          <t>23,89; 46,71</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 25,15</t>
+          <t>12,58; 25,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,28; 25,04</t>
+          <t>14,17; 25,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 25,52</t>
+          <t>14,04; 25,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,16; 32,07</t>
+          <t>19,08; 32,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,47; 24,53</t>
+          <t>13,76; 24,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,66; 26,02</t>
+          <t>14,84; 26,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,82; 23,44</t>
+          <t>13,0; 23,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,18; 28,78</t>
+          <t>15,62; 28,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,74; 22,78</t>
+          <t>14,23; 22,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,83; 23,5</t>
+          <t>16,09; 23,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 22,82</t>
+          <t>14,95; 22,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 27,83</t>
+          <t>18,75; 28,14</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 17,18</t>
+          <t>5,48; 16,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,65; 21,88</t>
+          <t>6,52; 22,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,6; 31,16</t>
+          <t>13,59; 31,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,3; 26,69</t>
+          <t>11,38; 27,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,65; 23,63</t>
+          <t>9,39; 23,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,92; 28,02</t>
+          <t>12,17; 27,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,36; 23,79</t>
+          <t>8,4; 23,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 30,82</t>
+          <t>13,8; 31,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,07; 17,31</t>
+          <t>9,09; 18,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,6; 22,34</t>
+          <t>11,67; 22,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,55; 23,36</t>
+          <t>12,76; 24,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,67; 26,53</t>
+          <t>14,18; 25,43</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,51</t>
+          <t>14,88; 19,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,15</t>
+          <t>18,19; 23,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,04; 20,65</t>
+          <t>16,09; 20,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,37; 36,88</t>
+          <t>21,98; 36,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,43; 22,15</t>
+          <t>17,52; 22,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,08; 23,07</t>
+          <t>18,29; 23,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,37; 18,88</t>
+          <t>14,18; 18,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,17; 27,16</t>
+          <t>20,85; 27,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,73; 20,27</t>
+          <t>16,8; 20,14</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,84; 22,37</t>
+          <t>18,72; 22,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,7; 19,14</t>
+          <t>15,69; 18,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,77; 30,89</t>
+          <t>22,72; 30,43</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>15171</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20920</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15843</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24852</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>31401</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42898</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33587</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>56253</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10258; 21171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15319; 28177</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10569; 22069</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18193; 32203</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14520; 28706</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>15409; 29048</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12066; 24785</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>22299; 41145</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>28690; 45532</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>32781; 52224</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>25152; 42914</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>44538; 69427</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>19430</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22903</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11996</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23432</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19061</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>23492</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>37287</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>34992</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>31057</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>46924</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>13756; 26527</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16406; 30937</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7935; 18453</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17287; 30348</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12133; 23956</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7540; 18617</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>13332; 25946</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>16139; 31058</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>28999; 46048</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>27392; 44547</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>23437; 40613</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>36947; 57613</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11471</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8846</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9596</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>17296</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>33062</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>23949</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19113</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>26892</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7013; 16666</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6856; 17323</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5399; 14129</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5874; 15105</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>15928; 29272</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7441; 18620</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5840; 15737</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>11873; 24137</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>25354; 41970</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>17049; 31940</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13449; 27283</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>19862; 36185</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>37685</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48643</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>46489</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>76381</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58910</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>76475</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>107552</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>81013</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>132225</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>29063; 46773</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38955; 58653</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37713; 56407</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>51100; 127106</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30479; 49213</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>48153; 71038</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>26699; 44921</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>43583; 69144</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>63347; 88751</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>93610; 122463</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>69197; 94942</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>104216; 203798</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>18853</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28645</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>26621</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28906</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28037</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>35977</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>42752</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>56682</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>52282</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>64883</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>13095; 26055</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>21134; 38441</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19127; 35073</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>22121; 37213</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>17510; 31141</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20935; 36828</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>18597; 33325</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>25396; 46346</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>32938; 52275</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>46711; 69557</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>41764; 62819</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>52236; 78376</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>7484</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7056</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13025</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12221</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>15299</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>18821</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>20851</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>22803</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>27520</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4105; 12358</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3514; 12168</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>8304; 19203</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>7843; 18612</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>6797; 17037</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>8915; 20318</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>5698; 15976</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>9936; 22838</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>13379; 26646</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>14835; 28488</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>16445; 31470</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>19981; 35829</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>109734</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>139638</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>122820</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>175387</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>147286</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>179309</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>245030</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>286924</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>239855</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>354697</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>95070; 125736</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>123395; 157792</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>108018; 140229</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>143737; 238947</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>119932; 154385</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>130765; 166175</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100665; 133451</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>156070; 205397</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>222367; 266568</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>260898; 311500</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>216717; 262216</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>318556; 426792</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP15-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 20,29</t>
+          <t>9,88; 21,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,03; 31,33</t>
+          <t>16,05; 31,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,72; 26,56</t>
+          <t>12,66; 27,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 30,83</t>
+          <t>17,69; 31,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,89; 29,43</t>
+          <t>16,24; 29,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,3; 32,62</t>
+          <t>17,66; 33,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,09; 24,84</t>
+          <t>11,93; 24,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 30,21</t>
+          <t>16,17; 30,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 22,55</t>
+          <t>13,69; 22,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 29,18</t>
+          <t>19,44; 29,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,75; 23,46</t>
+          <t>14,11; 23,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 28,85</t>
+          <t>18,82; 28,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,74; 30,36</t>
+          <t>15,61; 29,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 33,17</t>
+          <t>17,88; 32,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 17,46</t>
+          <t>7,05; 17,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,26; 32,05</t>
+          <t>18,36; 33,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 27,87</t>
+          <t>14,71; 28,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 19,24</t>
+          <t>7,79; 19,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 23,01</t>
+          <t>11,78; 23,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,89; 32,5</t>
+          <t>17,47; 33,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 26,56</t>
+          <t>16,78; 26,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,41; 23,44</t>
+          <t>14,02; 23,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 18,59</t>
+          <t>10,85; 18,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,42; 30,28</t>
+          <t>19,68; 29,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,41; 24,73</t>
+          <t>10,35; 24,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,96; 20,11</t>
+          <t>7,84; 20,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,73; 22,85</t>
+          <t>8,31; 21,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 29,13</t>
+          <t>11,09; 27,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 29,47</t>
+          <t>15,6; 28,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 21,43</t>
+          <t>9,09; 21,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 20,86</t>
+          <t>8,15; 21,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,59; 37,8</t>
+          <t>17,52; 38,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,21; 25,17</t>
+          <t>15,27; 25,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 18,46</t>
+          <t>10,12; 18,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 19,88</t>
+          <t>9,29; 19,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,16; 31,27</t>
+          <t>16,98; 31,05</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,48; 23,3</t>
+          <t>15,01; 23,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,9; 28,46</t>
+          <t>18,74; 28,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 25,23</t>
+          <t>16,84; 25,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,44; 58,3</t>
+          <t>23,01; 57,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,08; 24,35</t>
+          <t>14,84; 24,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,11; 31,14</t>
+          <t>21,25; 31,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,66; 21,3</t>
+          <t>12,6; 21,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,97; 31,68</t>
+          <t>19,85; 32,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,73; 22,03</t>
+          <t>16,2; 22,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,56; 28,2</t>
+          <t>21,54; 28,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,93; 21,85</t>
+          <t>16,01; 21,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,89; 46,71</t>
+          <t>24,08; 43,21</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,58; 25,02</t>
+          <t>12,66; 24,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,17; 25,77</t>
+          <t>13,83; 24,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 25,75</t>
+          <t>14,71; 26,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,08; 32,1</t>
+          <t>18,88; 31,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,76; 24,46</t>
+          <t>13,88; 25,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,84; 26,11</t>
+          <t>15,05; 25,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,0; 23,29</t>
+          <t>13,11; 23,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,62; 28,5</t>
+          <t>15,84; 29,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,23; 22,59</t>
+          <t>14,77; 22,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,09; 23,97</t>
+          <t>15,84; 23,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,49</t>
+          <t>15,49; 23,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,75; 28,14</t>
+          <t>18,66; 28,1</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 16,51</t>
+          <t>5,39; 17,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 22,57</t>
+          <t>6,57; 22,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,59; 31,43</t>
+          <t>14,02; 30,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,38; 27,02</t>
+          <t>11,37; 26,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 23,53</t>
+          <t>9,28; 23,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,17; 27,73</t>
+          <t>12,2; 27,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,4; 23,55</t>
+          <t>8,14; 22,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,8; 31,72</t>
+          <t>14,03; 32,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,09; 18,09</t>
+          <t>8,62; 17,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,67; 22,4</t>
+          <t>11,23; 21,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,76; 24,41</t>
+          <t>12,62; 24,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,18; 25,43</t>
+          <t>14,42; 25,77</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,88; 19,68</t>
+          <t>14,89; 19,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,19; 23,25</t>
+          <t>18,06; 22,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,09; 20,88</t>
+          <t>15,92; 20,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,98; 36,55</t>
+          <t>22,59; 37,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,52; 22,55</t>
+          <t>17,51; 22,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,29; 23,24</t>
+          <t>18,3; 23,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,18; 18,8</t>
+          <t>14,3; 18,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,85; 27,44</t>
+          <t>21,0; 26,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,8; 20,14</t>
+          <t>16,94; 20,4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,72; 22,35</t>
+          <t>18,98; 22,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,69; 18,98</t>
+          <t>15,66; 18,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,72; 30,43</t>
+          <t>22,81; 30,8</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10258; 21171</t>
+          <t>10315; 22031</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15319; 28177</t>
+          <t>14438; 28345</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10569; 22069</t>
+          <t>10520; 23038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18193; 32203</t>
+          <t>18481; 33198</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14520; 28706</t>
+          <t>15843; 28588</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15409; 29048</t>
+          <t>15725; 29696</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12066; 24785</t>
+          <t>11909; 24492</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22299; 41145</t>
+          <t>22026; 41047</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28690; 45532</t>
+          <t>27636; 45921</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32781; 52224</t>
+          <t>34800; 52830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25152; 42914</t>
+          <t>25802; 43596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44538; 69427</t>
+          <t>45296; 69045</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13756; 26527</t>
+          <t>13645; 25832</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16406; 30937</t>
+          <t>16677; 30052</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7935; 18453</t>
+          <t>7455; 18010</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17287; 30348</t>
+          <t>17380; 31510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12133; 23956</t>
+          <t>12649; 24279</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7540; 18617</t>
+          <t>7539; 18466</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13332; 25946</t>
+          <t>13286; 26309</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16139; 31058</t>
+          <t>16695; 31690</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28999; 46048</t>
+          <t>29089; 46587</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27392; 44547</t>
+          <t>26637; 44078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23437; 40613</t>
+          <t>23699; 40133</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36947; 57613</t>
+          <t>37440; 56950</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7013; 16666</t>
+          <t>6974; 16531</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6856; 17323</t>
+          <t>6753; 17350</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5399; 14129</t>
+          <t>5138; 13537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5874; 15105</t>
+          <t>5749; 14218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15928; 29272</t>
+          <t>15495; 28429</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7441; 18620</t>
+          <t>7901; 18391</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5840; 15737</t>
+          <t>6144; 16103</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11873; 24137</t>
+          <t>11189; 24888</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25354; 41970</t>
+          <t>25463; 43086</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17049; 31940</t>
+          <t>17516; 32328</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13449; 27283</t>
+          <t>12755; 26448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19862; 36185</t>
+          <t>19647; 35934</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29063; 46773</t>
+          <t>30127; 48007</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38955; 58653</t>
+          <t>38631; 57981</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37713; 56407</t>
+          <t>37647; 56685</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51100; 127106</t>
+          <t>50156; 126100</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30479; 49213</t>
+          <t>29995; 48739</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48153; 71038</t>
+          <t>48469; 71063</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26699; 44921</t>
+          <t>26567; 44466</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43583; 69144</t>
+          <t>43324; 70161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63347; 88751</t>
+          <t>65237; 90035</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93610; 122463</t>
+          <t>93542; 122881</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69197; 94942</t>
+          <t>69570; 94934</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>104216; 203798</t>
+          <t>105037; 188538</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13095; 26055</t>
+          <t>13181; 25382</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21134; 38441</t>
+          <t>20623; 36954</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19127; 35073</t>
+          <t>20036; 35439</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22121; 37213</t>
+          <t>21888; 36917</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17510; 31141</t>
+          <t>17662; 32272</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20935; 36828</t>
+          <t>21227; 36011</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18597; 33325</t>
+          <t>18753; 33973</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25396; 46346</t>
+          <t>25753; 47335</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32938; 52275</t>
+          <t>34173; 52530</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46711; 69557</t>
+          <t>45979; 68439</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41764; 62819</t>
+          <t>43261; 65054</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52236; 78376</t>
+          <t>51981; 78274</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4105; 12358</t>
+          <t>4037; 12952</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3514; 12168</t>
+          <t>3540; 12065</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8304; 19203</t>
+          <t>8563; 18915</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7843; 18612</t>
+          <t>7830; 18230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6797; 17037</t>
+          <t>6716; 16658</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8915; 20318</t>
+          <t>8937; 19896</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5698; 15976</t>
+          <t>5524; 15110</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9936; 22838</t>
+          <t>10101; 23077</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13379; 26646</t>
+          <t>12687; 26218</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14835; 28488</t>
+          <t>14286; 27778</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16445; 31470</t>
+          <t>16275; 31192</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19981; 35829</t>
+          <t>20312; 36304</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>95070; 125736</t>
+          <t>95134; 126607</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>123395; 157792</t>
+          <t>122558; 155563</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>108018; 140229</t>
+          <t>106902; 139568</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143737; 238947</t>
+          <t>147697; 245026</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>119932; 154385</t>
+          <t>119889; 151935</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>130765; 166175</t>
+          <t>130863; 166239</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>100665; 133451</t>
+          <t>101506; 132486</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>156070; 205397</t>
+          <t>157158; 200236</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>222367; 266568</t>
+          <t>224229; 270001</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>260898; 311500</t>
+          <t>264561; 315596</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>216717; 262216</t>
+          <t>216296; 261147</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>318556; 426792</t>
+          <t>319938; 431859</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP15-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24,68%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23,65%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>14,54%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23,26%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19,07%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,78%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 21,11</t>
+          <t>16,23; 29,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 31,52</t>
+          <t>17,27; 32,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 27,73</t>
+          <t>11,85; 24,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,69; 31,78</t>
+          <t>17,11; 31,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,24; 29,31</t>
+          <t>9,9; 20,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,66; 33,35</t>
+          <t>16,56; 31,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 24,54</t>
+          <t>12,76; 27,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,17; 30,14</t>
+          <t>18,08; 31,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 22,74</t>
+          <t>14,13; 22,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,44; 29,52</t>
+          <t>19,36; 30,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,11; 23,84</t>
+          <t>13,92; 23,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,82; 28,69</t>
+          <t>19,2; 29,41</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24,76%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>22,23%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>24,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,35%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,77%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,61; 29,56</t>
+          <t>14,18; 28,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,88; 32,22</t>
+          <t>8,09; 19,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 17,04</t>
+          <t>11,45; 23,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,36; 33,28</t>
+          <t>17,38; 33,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,71; 28,24</t>
+          <t>15,86; 30,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 19,08</t>
+          <t>17,95; 31,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,78; 23,33</t>
+          <t>7,33; 17,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 33,16</t>
+          <t>17,16; 31,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,78; 26,87</t>
+          <t>16,38; 26,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,02; 23,19</t>
+          <t>14,49; 23,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,85; 18,37</t>
+          <t>10,4; 18,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,68; 29,93</t>
+          <t>19,31; 29,97</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22,1%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26,39%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16,49%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,31%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14,3%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,5%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 24,53</t>
+          <t>15,7; 29,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 20,14</t>
+          <t>8,9; 21,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 21,89</t>
+          <t>7,81; 21,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,09; 27,41</t>
+          <t>16,29; 35,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,6; 28,62</t>
+          <t>10,5; 24,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 21,17</t>
+          <t>8,27; 20,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 21,35</t>
+          <t>8,33; 22,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 38,98</t>
+          <t>10,9; 28,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 25,84</t>
+          <t>15,15; 25,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 18,68</t>
+          <t>9,58; 18,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 19,27</t>
+          <t>9,59; 19,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,98; 31,05</t>
+          <t>16,04; 29,14</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,2%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25,83%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24,63%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>18,77%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23,6%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20,79%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35,04%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,01; 23,92</t>
+          <t>15,12; 23,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 28,13</t>
+          <t>21,05; 30,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 25,35</t>
+          <t>12,33; 21,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,01; 57,84</t>
+          <t>19,5; 31,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,84; 24,12</t>
+          <t>14,25; 23,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,25; 31,15</t>
+          <t>18,91; 28,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,6; 21,09</t>
+          <t>16,78; 25,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,85; 32,14</t>
+          <t>18,67; 29,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,2; 22,35</t>
+          <t>15,92; 22,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,54; 28,3</t>
+          <t>21,63; 28,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,01; 21,85</t>
+          <t>15,62; 21,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,08; 43,21</t>
+          <t>20,48; 28,37</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21,7%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>18,11%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19,2%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>19,55%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24,93%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,88%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,93%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,66; 24,38</t>
+          <t>13,47; 24,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,83; 24,77</t>
+          <t>14,66; 26,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,71; 26,02</t>
+          <t>12,82; 23,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,88; 31,84</t>
+          <t>15,88; 28,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,88; 25,35</t>
+          <t>12,61; 25,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,05; 25,53</t>
+          <t>14,28; 25,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,11; 23,74</t>
+          <t>14,04; 25,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,84; 29,11</t>
+          <t>18,76; 31,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,77; 22,7</t>
+          <t>14,74; 22,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,84; 23,58</t>
+          <t>15,83; 23,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,49; 23,29</t>
+          <t>14,75; 22,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,66; 28,1</t>
+          <t>18,75; 27,38</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18,83%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13,09%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>21,32%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 17,3</t>
+          <t>9,65; 23,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 22,38</t>
+          <t>11,92; 28,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 30,96</t>
+          <t>8,36; 23,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,37; 26,46</t>
+          <t>11,99; 30,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,28; 23,01</t>
+          <t>5,36; 17,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,2; 27,16</t>
+          <t>6,65; 21,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 22,28</t>
+          <t>13,6; 31,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,03; 32,05</t>
+          <t>11,69; 27,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,62; 17,8</t>
+          <t>9,07; 17,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 21,84</t>
+          <t>11,6; 22,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 24,2</t>
+          <t>12,55; 23,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,42; 25,77</t>
+          <t>14,12; 25,77</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16,49%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23,6%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>17,18%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20,58%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>18,29%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26,82%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,89; 19,82</t>
+          <t>17,43; 22,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,06; 22,93</t>
+          <t>18,08; 23,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,92; 20,78</t>
+          <t>14,37; 18,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,59; 37,48</t>
+          <t>20,92; 26,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,51; 22,19</t>
+          <t>14,82; 19,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,3; 23,25</t>
+          <t>18,26; 23,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,3; 18,67</t>
+          <t>16,04; 20,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,0; 26,75</t>
+          <t>19,64; 25,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,94; 20,4</t>
+          <t>16,73; 20,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,98; 22,64</t>
+          <t>18,84; 22,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,66; 18,91</t>
+          <t>15,7; 19,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,81; 30,8</t>
+          <t>21,29; 25,29</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>20920</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>15843</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21978</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10315; 22031</t>
+          <t>15834; 28792</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14438; 28345</t>
+          <t>15379; 29050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10520; 23038</t>
+          <t>11822; 24453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18481; 33198</t>
+          <t>20864; 38371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15843; 28588</t>
+          <t>10326; 21453</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15725; 29696</t>
+          <t>14897; 28142</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11909; 24492</t>
+          <t>10602; 23223</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22026; 41047</t>
+          <t>18614; 32207</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27636; 45921</t>
+          <t>28538; 45309</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34800; 52830</t>
+          <t>34656; 54334</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25802; 43596</t>
+          <t>25455; 42834</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45296; 69045</t>
+          <t>43174; 66146</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19061</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22903</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19061</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13645; 25832</t>
+          <t>12191; 24563</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16677; 30052</t>
+          <t>7825; 19118</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7455; 18010</t>
+          <t>12910; 26599</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17380; 31510</t>
+          <t>15888; 31043</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12649; 24279</t>
+          <t>13859; 26425</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7539; 18466</t>
+          <t>16740; 29722</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13286; 26309</t>
+          <t>7744; 18199</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16695; 31690</t>
+          <t>16569; 30570</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29089; 46587</t>
+          <t>28389; 46483</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26637; 44078</t>
+          <t>27541; 44217</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23699; 40133</t>
+          <t>22723; 39722</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37440; 56950</t>
+          <t>36285; 56317</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>11471</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8846</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6974; 16531</t>
+          <t>15598; 28954</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6753; 17350</t>
+          <t>7730; 18825</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5138; 13537</t>
+          <t>5893; 16240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5749; 14218</t>
+          <t>9278; 20412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15495; 28429</t>
+          <t>7075; 16642</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7901; 18391</t>
+          <t>7126; 17358</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6144; 16103</t>
+          <t>5148; 13779</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11189; 24888</t>
+          <t>5827; 15009</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25463; 43086</t>
+          <t>25259; 43021</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17516; 32328</t>
+          <t>16584; 31978</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12755; 26448</t>
+          <t>13167; 26559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19647; 35934</t>
+          <t>17715; 32175</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58910</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>48643</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>46489</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58910</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30127; 48007</t>
+          <t>30559; 47915</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38631; 57981</t>
+          <t>48028; 70190</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37647; 56685</t>
+          <t>25992; 44621</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50156; 126100</t>
+          <t>39389; 62690</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29995; 48739</t>
+          <t>28598; 47280</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48469; 71063</t>
+          <t>38966; 58677</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26567; 44466</t>
+          <t>37524; 57381</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43324; 70161</t>
+          <t>33383; 52075</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65237; 90035</t>
+          <t>64116; 89842</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93542; 122881</t>
+          <t>93917; 122596</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69570; 94934</t>
+          <t>67857; 94199</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>105037; 188538</t>
+          <t>77980; 108036</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28037</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>28645</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>26621</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28037</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60784</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13181; 25382</t>
+          <t>17143; 31228</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20623; 36954</t>
+          <t>20683; 36707</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20036; 35439</t>
+          <t>18344; 33534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21888; 36917</t>
+          <t>23542; 41826</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17662; 32272</t>
+          <t>13127; 26189</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21227; 36011</t>
+          <t>21298; 37345</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18753; 33973</t>
+          <t>19124; 34751</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25753; 47335</t>
+          <t>22113; 37467</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34173; 52530</t>
+          <t>34103; 52726</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45979; 68439</t>
+          <t>45957; 68207</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43261; 65054</t>
+          <t>41201; 63727</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51981; 78274</t>
+          <t>49891; 72850</t>
         </is>
       </c>
     </row>
@@ -2831,37 +2831,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14115</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>7056</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12221</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4037; 12952</t>
+          <t>6984; 17107</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3540; 12065</t>
+          <t>8735; 20531</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8563; 18915</t>
+          <t>5672; 16135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7830; 18230</t>
+          <t>8188; 20672</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6716; 16658</t>
+          <t>4010; 12862</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8937; 19896</t>
+          <t>3586; 11795</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5524; 15110</t>
+          <t>8306; 19036</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10101; 23077</t>
+          <t>8226; 19120</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12687; 26218</t>
+          <t>13360; 25489</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14286; 27778</t>
+          <t>14753; 28409</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16275; 31192</t>
+          <t>16176; 30109</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20312; 36304</t>
+          <t>19582; 35727</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>222</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>147286</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>139638</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>122820</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>147286</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>95134; 126607</t>
+          <t>119349; 151620</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>122558; 155563</t>
+          <t>129286; 165004</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106902; 139568</t>
+          <t>101984; 133990</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>147697; 245026</t>
+          <t>144108; 185006</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>119889; 151935</t>
+          <t>94657; 124634</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>130863; 166239</t>
+          <t>123922; 157116</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>101506; 132486</t>
+          <t>107706; 138658</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>157158; 200236</t>
+          <t>121784; 158048</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>224229; 270001</t>
+          <t>221410; 268239</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>264561; 315596</t>
+          <t>262525; 311769</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>216296; 261147</t>
+          <t>216892; 264391</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>319938; 431859</t>
+          <t>278684; 331048</t>
         </is>
       </c>
     </row>
